--- a/output/roomself_excel/9970.xlsx
+++ b/output/roomself_excel/9970.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>687924</v>
+        <v>150136</v>
       </c>
       <c r="D2" t="n">
-        <v>12952</v>
+        <v>3128</v>
       </c>
       <c r="E2" t="n">
-        <v>1237</v>
+        <v>344</v>
       </c>
       <c r="F2" t="n">
-        <v>1007</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>204578</v>
+        <v>150731</v>
       </c>
       <c r="D3" t="n">
-        <v>4600</v>
+        <v>3120</v>
       </c>
       <c r="E3" t="n">
-        <v>1007</v>
+        <v>353</v>
       </c>
       <c r="F3" t="n">
-        <v>427</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>306648</v>
+        <v>40506</v>
       </c>
       <c r="D4" t="n">
-        <v>7084</v>
+        <v>1964</v>
       </c>
       <c r="E4" t="n">
-        <v>968</v>
+        <v>150</v>
       </c>
       <c r="F4" t="n">
-        <v>865</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27393</v>
+        <v>237399</v>
       </c>
       <c r="D5" t="n">
-        <v>1864</v>
+        <v>4384</v>
       </c>
       <c r="E5" t="n">
-        <v>412</v>
+        <v>602</v>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>129456</v>
+        <v>204578</v>
       </c>
       <c r="D6" t="n">
-        <v>2880</v>
+        <v>4600</v>
       </c>
       <c r="E6" t="n">
-        <v>799</v>
+        <v>550</v>
       </c>
       <c r="F6" t="n">
-        <v>106</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29230</v>
+        <v>171800</v>
       </c>
       <c r="D7" t="n">
-        <v>1876</v>
+        <v>3612</v>
       </c>
       <c r="E7" t="n">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>154433</v>
+        <v>154298</v>
       </c>
       <c r="D8" t="n">
-        <v>3144</v>
+        <v>3156</v>
       </c>
       <c r="E8" t="n">
-        <v>332</v>
+        <v>447</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>153655</v>
+        <v>108885</v>
       </c>
       <c r="D9" t="n">
-        <v>3136</v>
+        <v>2728</v>
       </c>
       <c r="E9" t="n">
-        <v>389</v>
+        <v>443</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38254</v>
+        <v>28776</v>
       </c>
       <c r="D10" t="n">
-        <v>2060</v>
+        <v>1492</v>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28776</v>
+        <v>24235</v>
       </c>
       <c r="D11" t="n">
-        <v>1492</v>
+        <v>1264</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24235</v>
+        <v>25280</v>
       </c>
       <c r="D12" t="n">
-        <v>1264</v>
+        <v>1584</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25280</v>
+        <v>12190</v>
       </c>
       <c r="D13" t="n">
-        <v>1584</v>
+        <v>884</v>
       </c>
       <c r="E13" t="n">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>161382</v>
+        <v>10580</v>
       </c>
       <c r="D14" t="n">
-        <v>4692</v>
+        <v>828</v>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>154298</v>
+        <v>45784</v>
       </c>
       <c r="D15" t="n">
-        <v>3156</v>
+        <v>1720</v>
       </c>
       <c r="E15" t="n">
-        <v>447</v>
+        <v>252</v>
       </c>
       <c r="F15" t="n">
-        <v>373</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16">
@@ -774,17 +774,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>150731</v>
+        <v>129360</v>
       </c>
       <c r="D16" t="n">
-        <v>3120</v>
+        <v>3680</v>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>238</v>
       </c>
       <c r="F16" t="n">
         <v>16</v>
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>108885</v>
+        <v>44946</v>
       </c>
       <c r="D17" t="n">
-        <v>2728</v>
+        <v>1700</v>
       </c>
       <c r="E17" t="n">
-        <v>443</v>
+        <v>198</v>
       </c>
       <c r="F17" t="n">
-        <v>271</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>101888</v>
+        <v>38254</v>
       </c>
       <c r="D18" t="n">
-        <v>2616</v>
+        <v>2060</v>
       </c>
       <c r="E18" t="n">
-        <v>272</v>
+        <v>109</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>102700</v>
+        <v>30208</v>
       </c>
       <c r="D19" t="n">
-        <v>2620</v>
+        <v>1744</v>
       </c>
       <c r="E19" t="n">
-        <v>495</v>
+        <v>116</v>
       </c>
       <c r="F19" t="n">
-        <v>260</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12190</v>
+        <v>35872</v>
       </c>
       <c r="D21" t="n">
-        <v>884</v>
+        <v>1552</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -906,14 +906,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10580</v>
+        <v>148770</v>
       </c>
       <c r="D22" t="n">
-        <v>828</v>
+        <v>3284</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33048</v>
+        <v>113677</v>
       </c>
       <c r="D23" t="n">
-        <v>2124</v>
+        <v>2780</v>
       </c>
       <c r="E23" t="n">
-        <v>474</v>
+        <v>291</v>
       </c>
       <c r="F23" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7245</v>
+        <v>27393</v>
       </c>
       <c r="D24" t="n">
-        <v>712</v>
+        <v>1864</v>
       </c>
       <c r="E24" t="n">
-        <v>115</v>
+        <v>412</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>49140</v>
+        <v>129456</v>
       </c>
       <c r="D25" t="n">
-        <v>3372</v>
+        <v>2880</v>
       </c>
       <c r="E25" t="n">
-        <v>796</v>
+        <v>372</v>
       </c>
       <c r="F25" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>180868</v>
+        <v>29230</v>
       </c>
       <c r="D26" t="n">
-        <v>3464</v>
+        <v>1876</v>
       </c>
       <c r="E26" t="n">
-        <v>522</v>
+        <v>411</v>
       </c>
       <c r="F26" t="n">
-        <v>376</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>330994</v>
+        <v>154433</v>
       </c>
       <c r="D27" t="n">
-        <v>6388</v>
+        <v>3144</v>
       </c>
       <c r="E27" t="n">
-        <v>708</v>
+        <v>332</v>
       </c>
       <c r="F27" t="n">
-        <v>538</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>146687</v>
+        <v>153655</v>
       </c>
       <c r="D28" t="n">
-        <v>3552</v>
+        <v>3136</v>
       </c>
       <c r="E28" t="n">
-        <v>317</v>
+        <v>389</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>44946</v>
+        <v>134848</v>
       </c>
       <c r="D29" t="n">
-        <v>1700</v>
+        <v>4304</v>
       </c>
       <c r="E29" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>35872</v>
+        <v>120876</v>
       </c>
       <c r="D30" t="n">
-        <v>1552</v>
+        <v>3076</v>
       </c>
       <c r="E30" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1104,20 +1104,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>45784</v>
+        <v>27144</v>
       </c>
       <c r="D31" t="n">
-        <v>1720</v>
+        <v>2248</v>
       </c>
       <c r="E31" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>170669</v>
+        <v>101888</v>
       </c>
       <c r="D32" t="n">
-        <v>4888</v>
+        <v>2616</v>
       </c>
       <c r="E32" t="n">
-        <v>720</v>
+        <v>272</v>
       </c>
       <c r="F32" t="n">
-        <v>400</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>49408</v>
+        <v>102700</v>
       </c>
       <c r="D33" t="n">
-        <v>1796</v>
+        <v>2620</v>
       </c>
       <c r="E33" t="n">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="F33" t="n">
-        <v>226</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34">
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27136</v>
+        <v>33048</v>
       </c>
       <c r="D34" t="n">
-        <v>1448</v>
+        <v>2124</v>
       </c>
       <c r="E34" t="n">
-        <v>106</v>
+        <v>474</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>64985</v>
+        <v>7245</v>
       </c>
       <c r="D35" t="n">
-        <v>2088</v>
+        <v>712</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>168480</v>
+        <v>49140</v>
       </c>
       <c r="D36" t="n">
-        <v>3312</v>
+        <v>3372</v>
       </c>
       <c r="E36" t="n">
-        <v>468</v>
+        <v>796</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
@@ -1236,20 +1236,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>148770</v>
+        <v>180868</v>
       </c>
       <c r="D37" t="n">
-        <v>3284</v>
+        <v>3464</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>522</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
     </row>
     <row r="38">
@@ -1262,15 +1262,169 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>330994</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6388</v>
+      </c>
+      <c r="E38" t="n">
+        <v>302</v>
+      </c>
+      <c r="F38" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>146687</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3552</v>
+      </c>
+      <c r="E39" t="n">
+        <v>317</v>
+      </c>
+      <c r="F39" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>170669</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4888</v>
+      </c>
+      <c r="E40" t="n">
+        <v>123</v>
+      </c>
+      <c r="F40" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>49408</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1796</v>
+      </c>
+      <c r="E41" t="n">
+        <v>193</v>
+      </c>
+      <c r="F41" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>27136</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1448</v>
+      </c>
+      <c r="E42" t="n">
+        <v>106</v>
+      </c>
+      <c r="F42" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>64985</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2088</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>168480</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3312</v>
+      </c>
+      <c r="E44" t="n">
+        <v>468</v>
+      </c>
+      <c r="F44" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
         <v>62640</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D45" t="n">
         <v>2008</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E45" t="n">
         <v>270</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F45" t="n">
         <v>16</v>
       </c>
     </row>

--- a/output/roomself_excel/9970.xlsx
+++ b/output/roomself_excel/9970.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>3128</v>
       </c>
-      <c r="E2" t="n">
-        <v>344</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,23 @@
       <c r="D3" t="n">
         <v>3120</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>353</v>
       </c>
-      <c r="F3" t="n">
-        <v>16</v>
-      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +576,15 @@
       <c r="D4" t="n">
         <v>1964</v>
       </c>
-      <c r="E4" t="n">
-        <v>150</v>
-      </c>
-      <c r="F4" t="n">
-        <v>16</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +601,38 @@
       <c r="D5" t="n">
         <v>4384</v>
       </c>
-      <c r="E5" t="n">
-        <v>602</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>419</v>
+        <v>571</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>403</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>16</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +650,31 @@
       <c r="D6" t="n">
         <v>4600</v>
       </c>
-      <c r="E6" t="n">
-        <v>550</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>427</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>534</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +691,31 @@
       <c r="D7" t="n">
         <v>3612</v>
       </c>
-      <c r="E7" t="n">
-        <v>436</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>176</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +732,31 @@
       <c r="D8" t="n">
         <v>3156</v>
       </c>
-      <c r="E8" t="n">
-        <v>447</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>373</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>358</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +773,31 @@
       <c r="D9" t="n">
         <v>2728</v>
       </c>
-      <c r="E9" t="n">
-        <v>443</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>271</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>255</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +814,15 @@
       <c r="D10" t="n">
         <v>1492</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +839,15 @@
       <c r="D11" t="n">
         <v>1264</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +864,15 @@
       <c r="D12" t="n">
         <v>1584</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +889,15 @@
       <c r="D13" t="n">
         <v>884</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +914,15 @@
       <c r="D14" t="n">
         <v>828</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +939,31 @@
       <c r="D15" t="n">
         <v>1720</v>
       </c>
-      <c r="E15" t="n">
-        <v>252</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>210</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>236</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +980,23 @@
       <c r="D16" t="n">
         <v>3680</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>238</v>
       </c>
-      <c r="F16" t="n">
-        <v>16</v>
-      </c>
+      <c r="G16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1013,23 @@
       <c r="D17" t="n">
         <v>1700</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>198</v>
       </c>
-      <c r="F17" t="n">
-        <v>16</v>
-      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1046,23 @@
       <c r="D18" t="n">
         <v>2060</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>109</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>15</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1079,23 @@
       <c r="D19" t="n">
         <v>1744</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>116</v>
       </c>
-      <c r="F19" t="n">
-        <v>16</v>
-      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1112,23 @@
       <c r="D20" t="n">
         <v>2348</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>267</v>
       </c>
-      <c r="F20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1145,23 @@
       <c r="D21" t="n">
         <v>1552</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>152</v>
       </c>
-      <c r="F21" t="n">
-        <v>16</v>
-      </c>
+      <c r="G21" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1178,23 @@
       <c r="D22" t="n">
         <v>3284</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1211,23 @@
       <c r="D23" t="n">
         <v>2780</v>
       </c>
-      <c r="E23" t="n">
-        <v>291</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="G23" t="n">
+        <v>16</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1244,31 @@
       <c r="D24" t="n">
         <v>1864</v>
       </c>
-      <c r="E24" t="n">
-        <v>412</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>85</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="G24" t="n">
+        <v>16</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>69</v>
+      </c>
+      <c r="J24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1285,23 @@
       <c r="D25" t="n">
         <v>2880</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>372</v>
       </c>
-      <c r="F25" t="n">
-        <v>16</v>
-      </c>
+      <c r="G25" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1318,31 @@
       <c r="D26" t="n">
         <v>1876</v>
       </c>
-      <c r="E26" t="n">
-        <v>411</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>90</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="G26" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>74</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1359,23 @@
       <c r="D27" t="n">
         <v>3144</v>
       </c>
-      <c r="E27" t="n">
-        <v>332</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1392,23 @@
       <c r="D28" t="n">
         <v>3136</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>389</v>
       </c>
-      <c r="F28" t="n">
-        <v>16</v>
-      </c>
+      <c r="G28" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1425,23 @@
       <c r="D29" t="n">
         <v>4304</v>
       </c>
-      <c r="E29" t="n">
-        <v>263</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>102</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1458,15 @@
       <c r="D30" t="n">
         <v>3076</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1483,15 @@
       <c r="D31" t="n">
         <v>2248</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1508,23 @@
       <c r="D32" t="n">
         <v>2616</v>
       </c>
-      <c r="E32" t="n">
-        <v>272</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="G32" t="n">
+        <v>15</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1541,23 @@
       <c r="D33" t="n">
         <v>2620</v>
       </c>
-      <c r="E33" t="n">
-        <v>495</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F33" t="n">
         <v>260</v>
       </c>
+      <c r="G33" t="n">
+        <v>16</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1574,31 @@
       <c r="D34" t="n">
         <v>2124</v>
       </c>
-      <c r="E34" t="n">
-        <v>474</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>86</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G34" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>459</v>
+      </c>
+      <c r="J34" t="n">
+        <v>14</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1615,23 @@
       <c r="D35" t="n">
         <v>712</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>115</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>14</v>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1223,12 +1648,31 @@
       <c r="D36" t="n">
         <v>3372</v>
       </c>
-      <c r="E36" t="n">
-        <v>796</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F36" t="n">
-        <v>77</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G36" t="n">
+        <v>16</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>780</v>
+      </c>
+      <c r="J36" t="n">
+        <v>14</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1245,12 +1689,31 @@
       <c r="D37" t="n">
         <v>3464</v>
       </c>
-      <c r="E37" t="n">
-        <v>522</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>376</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="G37" t="n">
+        <v>16</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>506</v>
+      </c>
+      <c r="J37" t="n">
+        <v>16</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1267,12 +1730,31 @@
       <c r="D38" t="n">
         <v>6388</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>302</v>
       </c>
-      <c r="F38" t="n">
-        <v>16</v>
-      </c>
+      <c r="G38" t="n">
+        <v>16</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>415</v>
+      </c>
+      <c r="J38" t="n">
+        <v>15</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1289,12 +1771,23 @@
       <c r="D39" t="n">
         <v>3552</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>317</v>
       </c>
-      <c r="F39" t="n">
-        <v>16</v>
-      </c>
+      <c r="G39" t="n">
+        <v>16</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1311,12 +1804,23 @@
       <c r="D40" t="n">
         <v>4888</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>123</v>
       </c>
-      <c r="F40" t="n">
-        <v>16</v>
-      </c>
+      <c r="G40" t="n">
+        <v>16</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1333,12 +1837,23 @@
       <c r="D41" t="n">
         <v>1796</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>193</v>
       </c>
-      <c r="F41" t="n">
-        <v>16</v>
-      </c>
+      <c r="G41" t="n">
+        <v>16</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1355,12 +1870,23 @@
       <c r="D42" t="n">
         <v>1448</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>106</v>
       </c>
-      <c r="F42" t="n">
-        <v>16</v>
-      </c>
+      <c r="G42" t="n">
+        <v>16</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1377,12 +1903,15 @@
       <c r="D43" t="n">
         <v>2088</v>
       </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1399,12 +1928,31 @@
       <c r="D44" t="n">
         <v>3312</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>468</v>
       </c>
-      <c r="F44" t="n">
-        <v>16</v>
-      </c>
+      <c r="G44" t="n">
+        <v>16</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>360</v>
+      </c>
+      <c r="J44" t="n">
+        <v>15</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1421,12 +1969,31 @@
       <c r="D45" t="n">
         <v>2008</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
         <v>270</v>
       </c>
-      <c r="F45" t="n">
-        <v>16</v>
-      </c>
+      <c r="G45" t="n">
+        <v>16</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>232</v>
+      </c>
+      <c r="J45" t="n">
+        <v>15</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
